--- a/VMIT/PYTHON/VMIT - Day 5.xlsx
+++ b/VMIT/PYTHON/VMIT - Day 5.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Genplus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A2FA75-B0B1-4429-A405-60E1E74F5C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EFDA69-EDC6-4D79-A7C8-5BFBD1EBFECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D5F313DE-F3B9-4052-84D8-DC9AA2346115}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="E&amp;C" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>Topic</t>
   </si>
@@ -247,6 +248,30 @@
 stack.append(10)   # push
 stack.append(20)
 print(stack.pop())   # 20</t>
+  </si>
+  <si>
+    <t>Use in Electronics &amp; Communication Engineering (ECE) Domain</t>
+  </si>
+  <si>
+    <t>Singly Linked List Implementation</t>
+  </si>
+  <si>
+    <t>Used to manage dynamically changing packets, device nodes, routing tables, or task lists in embedded systems where memory-efficient insertion/deletion is needed. Example: storing active sensor nodes in an IoT network.</t>
+  </si>
+  <si>
+    <t>Used in microcontrollers and processors for function calls, interrupt handling, return addresses, and expression evaluation in signal-processing firmware. Example: nested interrupt service routines use stack memory.</t>
+  </si>
+  <si>
+    <t>Widely used in UART, SPI, CAN, and network communication systems for buffering incoming/outgoing data packets in FIFO order. Example: printer data queue or serial port receive queue.</t>
+  </si>
+  <si>
+    <t>Useful in simulations of communication systems where fast insertion/removal is needed at both ends. Example: modeling packet arrivals and departures in a router buffer.</t>
+  </si>
+  <si>
+    <t>Used in firmware diagnostics and data-stream analysis to detect loops, repeated signal frames, or locate midpoint in linked sensor data chains. Example: detecting circular references in memory structures.</t>
+  </si>
+  <si>
+    <t>Extremely common in ADC/DAC systems, DSP, UART receive/transmit buffers, audio streaming, radar sampling, and real-time data logging where continuous overwrite is required. Example: storing latest 1024 sensor samples for filtering.</t>
   </si>
 </sst>
 </file>
@@ -275,7 +300,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,6 +310,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -301,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -316,6 +347,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -786,4 +820,75 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E793121-6107-4F0D-BD27-A3A6A5DAB5C0}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="51" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="74.109375" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="51" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="28.8">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="57.6">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="57.6">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="57.6">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="43.2">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="57.6">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="72">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>